--- a/Data/TransactionData.xlsx
+++ b/Data/TransactionData.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <x:si>
     <x:t>ClientName</x:t>
   </x:si>
@@ -73,6 +73,9 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
+    <x:t>System exception: Object reference not set to an instance of an object. at Source: Process\Orchestrator\Orchestrator_GetMachines.xaml - Invoke Workflow File: Add Data Row</x:t>
+  </x:si>
+  <x:si>
     <x:t>Beneration</x:t>
   </x:si>
   <x:si>
@@ -97,7 +100,7 @@
     <x:t>Failed</x:t>
   </x:si>
   <x:si>
-    <x:t>Business exception: Something happend during authentication... at Source: Orchestrator_GetFolders - Invoke Workflow File (Process\Orchestrator\Orchestrator_GetFolders.xaml): Throw - Not Cloud</x:t>
+    <x:t>Business exception: Something happend during authentication... at Source: Orchestrator_CloudAuthentication - Invoke Workflow File (Process\Orchestrator\Orchestrator_CloudAuthentication.xaml): Throw - Not Cloud</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -506,7 +509,7 @@
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:BS234"/>
-  <x:sheetFormatPr defaultColWidth="133.76875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <x:sheetFormatPr defaultColWidth="160.061875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:cols>
     <x:col min="1" max="1" width="10.554688" style="0" bestFit="1" customWidth="1"/>
     <x:col min="2" max="2" width="54.777344" style="0" bestFit="1" customWidth="1"/>
@@ -621,6 +624,9 @@
       <x:c r="G2" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="J2" s="2" t="s"/>
       <x:c r="K2" s="2" t="s"/>
       <x:c r="L2" s="2" t="s"/>
@@ -686,16 +692,16 @@
     </x:row>
     <x:row r="3" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
         <x:v>13</x:v>
@@ -705,6 +711,9 @@
       </x:c>
       <x:c r="G3" s="0" t="s">
         <x:v>14</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J3" s="2" t="s"/>
       <x:c r="K3" s="2" t="s"/>
@@ -771,28 +780,28 @@
     </x:row>
     <x:row r="4" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F4" s="0" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="J4" s="2" t="s"/>
       <x:c r="K4" s="2" t="s"/>

--- a/Data/TransactionData.xlsx
+++ b/Data/TransactionData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <x:workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LuisRamos\OneDrive - Roboyo Global\Documents\UiPath\Personal\BotMonitor\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F20CF062-B9B6-419A-B3CA-464A5EF81BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69764614-BCE0-4C87-9037-A1B086715E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <x:bookViews>
     <x:workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="0" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </x:bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <x:si>
     <x:t>ClientName</x:t>
   </x:si>
@@ -55,34 +55,25 @@
     <x:t>TicketId</x:t>
   </x:si>
   <x:si>
-    <x:t>DawnFoods</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://cloud.uipath.com/dawnfoods/Prod/orchestrator_/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cloud</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Prod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Standard</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Success</x:t>
-  </x:si>
-  <x:si>
-    <x:t>System exception: Object reference not set to an instance of an object. at Source: Process\Orchestrator\Orchestrator_GetMachines.xaml - Invoke Workflow File: Add Data Row</x:t>
-  </x:si>
-  <x:si>
     <x:t>Beneration</x:t>
   </x:si>
   <x:si>
     <x:t>https://cloud.uipath.com/beneration/Production/orchestrator_/</x:t>
   </x:si>
   <x:si>
+    <x:t>Cloud</x:t>
+  </x:si>
+  <x:si>
     <x:t>Production</x:t>
+  </x:si>
+  <x:si>
+    <x:t>App</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Success</x:t>
+  </x:si>
+  <x:si>
+    <x:t>System exception: Object reference not set to an instance of an object. at Source: Orchestrator_CloudAuthentication - Invoke Workflow File (Process\Orchestrator\Orchestrator_CloudAuthentication.xaml): If</x:t>
   </x:si>
   <x:si>
     <x:t>CNB</x:t>
@@ -94,13 +85,46 @@
     <x:t>cnbfl_dev</x:t>
   </x:si>
   <x:si>
-    <x:t>App</x:t>
-  </x:si>
-  <x:si>
     <x:t>Failed</x:t>
   </x:si>
   <x:si>
-    <x:t>Business exception: Something happend during authentication... at Source: Orchestrator_CloudAuthentication - Invoke Workflow File (Process\Orchestrator\Orchestrator_CloudAuthentication.xaml): Throw - Not Cloud</x:t>
+    <x:t>Business exception: Skipping Account at Source: Throw</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CNB_Prd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://cloud.uipath.com/cnbfl/cnbfl/orchestrator_/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cnbfl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DawnFoods</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://cloud.uipath.com/dawnfoods/Prod/orchestrator_/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Standard</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Altria</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://uipathprod.altria.net/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OnPrem</x:t>
+  </x:si>
+  <x:si>
+    <x:t>default</x:t>
+  </x:si>
+  <x:si>
+    <x:t>System exception: Could not find the asset 'Altria_ClientID'. Error code: 1002; Asset name: Altria_ClientID at Source: Orchestrator_CloudAuthentication - Invoke Workflow File (Process\Orchestrator\Orchestrator_CloudAuthentication.xaml): Get Credential</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -508,13 +532,15 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:BS234"/>
-  <x:sheetFormatPr defaultColWidth="160.061875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <x:dimension ref="A1:BS233"/>
+  <x:sheetFormatPr defaultColWidth="255" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <x:cols>
     <x:col min="1" max="1" width="10.554688" style="0" bestFit="1" customWidth="1"/>
     <x:col min="2" max="2" width="54.777344" style="0" bestFit="1" customWidth="1"/>
     <x:col min="3" max="3" width="15.441406" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="4" max="6" width="11.554688" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.554688" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18.109375" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11.554688" style="0" customWidth="1"/>
     <x:col min="7" max="8" width="29.109375" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="0" style="0" hidden="1" customWidth="1"/>
   </x:cols>
@@ -707,13 +733,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="F3" s="0" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J3" s="2" t="s"/>
       <x:c r="K3" s="2" t="s"/>
@@ -780,28 +806,28 @@
     </x:row>
     <x:row r="4" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F4" s="0" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="J4" s="2" t="s"/>
       <x:c r="K4" s="2" t="s"/>
@@ -867,6 +893,30 @@
       <x:c r="BS4" s="5" t="s"/>
     </x:row>
     <x:row r="5" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="A5" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="J5" s="2" t="s"/>
       <x:c r="K5" s="2" t="s"/>
       <x:c r="L5" s="2" t="s"/>
@@ -931,6 +981,30 @@
       <x:c r="BS5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="A6" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
       <x:c r="J6" s="2" t="s"/>
       <x:c r="K6" s="2" t="s"/>
       <x:c r="L6" s="2" t="s"/>
@@ -3043,6 +3117,15 @@
       <x:c r="BS38" s="5" t="s"/>
     </x:row>
     <x:row r="39" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <x:c r="A39" s="5" t="s"/>
+      <x:c r="B39" s="7" t="s"/>
+      <x:c r="C39" s="6" t="s"/>
+      <x:c r="D39" s="6" t="s"/>
+      <x:c r="E39" s="6" t="s"/>
+      <x:c r="F39" s="6" t="s"/>
+      <x:c r="G39" s="2" t="s"/>
+      <x:c r="H39" s="2" t="s"/>
+      <x:c r="I39" s="2" t="s"/>
       <x:c r="J39" s="2" t="s"/>
       <x:c r="K39" s="2" t="s"/>
       <x:c r="L39" s="2" t="s"/>
@@ -3108,11 +3191,11 @@
     </x:row>
     <x:row r="40" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A40" s="5" t="s"/>
-      <x:c r="B40" s="7" t="s"/>
+      <x:c r="B40" s="5" t="s"/>
       <x:c r="C40" s="6" t="s"/>
-      <x:c r="D40" s="6" t="s"/>
-      <x:c r="E40" s="6" t="s"/>
-      <x:c r="F40" s="6" t="s"/>
+      <x:c r="D40" s="9" t="s"/>
+      <x:c r="E40" s="9" t="s"/>
+      <x:c r="F40" s="9" t="s"/>
       <x:c r="G40" s="2" t="s"/>
       <x:c r="H40" s="2" t="s"/>
       <x:c r="I40" s="2" t="s"/>
@@ -3183,9 +3266,9 @@
       <x:c r="A41" s="5" t="s"/>
       <x:c r="B41" s="5" t="s"/>
       <x:c r="C41" s="6" t="s"/>
-      <x:c r="D41" s="9" t="s"/>
-      <x:c r="E41" s="9" t="s"/>
-      <x:c r="F41" s="9" t="s"/>
+      <x:c r="D41" s="6" t="s"/>
+      <x:c r="E41" s="6" t="s"/>
+      <x:c r="F41" s="6" t="s"/>
       <x:c r="G41" s="2" t="s"/>
       <x:c r="H41" s="2" t="s"/>
       <x:c r="I41" s="2" t="s"/>
@@ -3256,9 +3339,9 @@
       <x:c r="A42" s="5" t="s"/>
       <x:c r="B42" s="5" t="s"/>
       <x:c r="C42" s="6" t="s"/>
-      <x:c r="D42" s="6" t="s"/>
-      <x:c r="E42" s="6" t="s"/>
-      <x:c r="F42" s="6" t="s"/>
+      <x:c r="D42" s="8" t="s"/>
+      <x:c r="E42" s="8" t="s"/>
+      <x:c r="F42" s="8" t="s"/>
       <x:c r="G42" s="2" t="s"/>
       <x:c r="H42" s="2" t="s"/>
       <x:c r="I42" s="2" t="s"/>
@@ -3329,9 +3412,9 @@
       <x:c r="A43" s="5" t="s"/>
       <x:c r="B43" s="5" t="s"/>
       <x:c r="C43" s="6" t="s"/>
-      <x:c r="D43" s="8" t="s"/>
-      <x:c r="E43" s="8" t="s"/>
-      <x:c r="F43" s="8" t="s"/>
+      <x:c r="D43" s="6" t="s"/>
+      <x:c r="E43" s="6" t="s"/>
+      <x:c r="F43" s="6" t="s"/>
       <x:c r="G43" s="2" t="s"/>
       <x:c r="H43" s="2" t="s"/>
       <x:c r="I43" s="2" t="s"/>
@@ -3405,10 +3488,6 @@
       <x:c r="D44" s="6" t="s"/>
       <x:c r="E44" s="6" t="s"/>
       <x:c r="F44" s="6" t="s"/>
-      <x:c r="G44" s="2" t="s"/>
-      <x:c r="H44" s="2" t="s"/>
-      <x:c r="I44" s="2" t="s"/>
-      <x:c r="J44" s="2" t="s"/>
       <x:c r="K44" s="2" t="s"/>
       <x:c r="L44" s="2" t="s"/>
       <x:c r="M44" s="2" t="s"/>
@@ -3473,11 +3552,15 @@
     </x:row>
     <x:row r="45" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A45" s="5" t="s"/>
-      <x:c r="B45" s="5" t="s"/>
+      <x:c r="B45" s="7" t="s"/>
       <x:c r="C45" s="6" t="s"/>
       <x:c r="D45" s="6" t="s"/>
       <x:c r="E45" s="6" t="s"/>
       <x:c r="F45" s="6" t="s"/>
+      <x:c r="G45" s="2" t="s"/>
+      <x:c r="H45" s="2" t="s"/>
+      <x:c r="I45" s="2" t="s"/>
+      <x:c r="J45" s="2" t="s"/>
       <x:c r="K45" s="2" t="s"/>
       <x:c r="L45" s="2" t="s"/>
       <x:c r="M45" s="2" t="s"/>
@@ -3542,7 +3625,7 @@
     </x:row>
     <x:row r="46" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A46" s="5" t="s"/>
-      <x:c r="B46" s="7" t="s"/>
+      <x:c r="B46" s="5" t="s"/>
       <x:c r="C46" s="6" t="s"/>
       <x:c r="D46" s="6" t="s"/>
       <x:c r="E46" s="6" t="s"/>
@@ -4199,11 +4282,11 @@
     </x:row>
     <x:row r="55" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A55" s="5" t="s"/>
-      <x:c r="B55" s="5" t="s"/>
+      <x:c r="B55" s="7" t="s"/>
       <x:c r="C55" s="6" t="s"/>
-      <x:c r="D55" s="6" t="s"/>
-      <x:c r="E55" s="6" t="s"/>
-      <x:c r="F55" s="6" t="s"/>
+      <x:c r="D55" s="9" t="s"/>
+      <x:c r="E55" s="9" t="s"/>
+      <x:c r="F55" s="9" t="s"/>
       <x:c r="G55" s="2" t="s"/>
       <x:c r="H55" s="2" t="s"/>
       <x:c r="I55" s="2" t="s"/>
@@ -4272,11 +4355,11 @@
     </x:row>
     <x:row r="56" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A56" s="5" t="s"/>
-      <x:c r="B56" s="7" t="s"/>
+      <x:c r="B56" s="5" t="s"/>
       <x:c r="C56" s="6" t="s"/>
-      <x:c r="D56" s="9" t="s"/>
-      <x:c r="E56" s="9" t="s"/>
-      <x:c r="F56" s="9" t="s"/>
+      <x:c r="D56" s="6" t="s"/>
+      <x:c r="E56" s="6" t="s"/>
+      <x:c r="F56" s="6" t="s"/>
       <x:c r="G56" s="2" t="s"/>
       <x:c r="H56" s="2" t="s"/>
       <x:c r="I56" s="2" t="s"/>
@@ -4345,7 +4428,7 @@
     </x:row>
     <x:row r="57" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A57" s="5" t="s"/>
-      <x:c r="B57" s="5" t="s"/>
+      <x:c r="B57" s="7" t="s"/>
       <x:c r="C57" s="6" t="s"/>
       <x:c r="D57" s="6" t="s"/>
       <x:c r="E57" s="6" t="s"/>
@@ -4491,7 +4574,7 @@
     </x:row>
     <x:row r="59" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A59" s="5" t="s"/>
-      <x:c r="B59" s="7" t="s"/>
+      <x:c r="B59" s="5" t="s"/>
       <x:c r="C59" s="6" t="s"/>
       <x:c r="D59" s="6" t="s"/>
       <x:c r="E59" s="6" t="s"/>
@@ -5149,10 +5232,7 @@
     <x:row r="68" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A68" s="5" t="s"/>
       <x:c r="B68" s="5" t="s"/>
-      <x:c r="C68" s="6" t="s"/>
-      <x:c r="D68" s="6" t="s"/>
-      <x:c r="E68" s="6" t="s"/>
-      <x:c r="F68" s="6" t="s"/>
+      <x:c r="C68" s="9" t="s"/>
       <x:c r="G68" s="2" t="s"/>
       <x:c r="H68" s="2" t="s"/>
       <x:c r="I68" s="2" t="s"/>
@@ -5222,7 +5302,10 @@
     <x:row r="69" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A69" s="5" t="s"/>
       <x:c r="B69" s="5" t="s"/>
-      <x:c r="C69" s="9" t="s"/>
+      <x:c r="C69" s="6" t="s"/>
+      <x:c r="D69" s="6" t="s"/>
+      <x:c r="E69" s="6" t="s"/>
+      <x:c r="F69" s="6" t="s"/>
       <x:c r="G69" s="2" t="s"/>
       <x:c r="H69" s="2" t="s"/>
       <x:c r="I69" s="2" t="s"/>
@@ -5658,9 +5741,9 @@
       <x:c r="A75" s="5" t="s"/>
       <x:c r="B75" s="5" t="s"/>
       <x:c r="C75" s="6" t="s"/>
-      <x:c r="D75" s="6" t="s"/>
-      <x:c r="E75" s="6" t="s"/>
-      <x:c r="F75" s="6" t="s"/>
+      <x:c r="D75" s="8" t="s"/>
+      <x:c r="E75" s="8" t="s"/>
+      <x:c r="F75" s="8" t="s"/>
       <x:c r="G75" s="2" t="s"/>
       <x:c r="H75" s="2" t="s"/>
       <x:c r="I75" s="2" t="s"/>
@@ -5729,11 +5812,11 @@
     </x:row>
     <x:row r="76" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A76" s="5" t="s"/>
-      <x:c r="B76" s="5" t="s"/>
+      <x:c r="B76" s="7" t="s"/>
       <x:c r="C76" s="6" t="s"/>
-      <x:c r="D76" s="8" t="s"/>
-      <x:c r="E76" s="8" t="s"/>
-      <x:c r="F76" s="8" t="s"/>
+      <x:c r="D76" s="6" t="s"/>
+      <x:c r="E76" s="6" t="s"/>
+      <x:c r="F76" s="6" t="s"/>
       <x:c r="G76" s="2" t="s"/>
       <x:c r="H76" s="2" t="s"/>
       <x:c r="I76" s="2" t="s"/>
@@ -5802,7 +5885,7 @@
     </x:row>
     <x:row r="77" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A77" s="5" t="s"/>
-      <x:c r="B77" s="7" t="s"/>
+      <x:c r="B77" s="5" t="s"/>
       <x:c r="C77" s="6" t="s"/>
       <x:c r="D77" s="6" t="s"/>
       <x:c r="E77" s="6" t="s"/>
@@ -5877,9 +5960,9 @@
       <x:c r="A78" s="5" t="s"/>
       <x:c r="B78" s="5" t="s"/>
       <x:c r="C78" s="6" t="s"/>
-      <x:c r="D78" s="6" t="s"/>
-      <x:c r="E78" s="6" t="s"/>
-      <x:c r="F78" s="6" t="s"/>
+      <x:c r="D78" s="8" t="s"/>
+      <x:c r="E78" s="8" t="s"/>
+      <x:c r="F78" s="8" t="s"/>
       <x:c r="G78" s="2" t="s"/>
       <x:c r="H78" s="2" t="s"/>
       <x:c r="I78" s="2" t="s"/>
@@ -5950,9 +6033,9 @@
       <x:c r="A79" s="5" t="s"/>
       <x:c r="B79" s="5" t="s"/>
       <x:c r="C79" s="6" t="s"/>
-      <x:c r="D79" s="8" t="s"/>
-      <x:c r="E79" s="8" t="s"/>
-      <x:c r="F79" s="8" t="s"/>
+      <x:c r="D79" s="6" t="s"/>
+      <x:c r="E79" s="6" t="s"/>
+      <x:c r="F79" s="6" t="s"/>
       <x:c r="G79" s="2" t="s"/>
       <x:c r="H79" s="2" t="s"/>
       <x:c r="I79" s="2" t="s"/>
@@ -6021,11 +6104,11 @@
     </x:row>
     <x:row r="80" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A80" s="5" t="s"/>
-      <x:c r="B80" s="5" t="s"/>
+      <x:c r="B80" s="7" t="s"/>
       <x:c r="C80" s="6" t="s"/>
-      <x:c r="D80" s="6" t="s"/>
-      <x:c r="E80" s="6" t="s"/>
-      <x:c r="F80" s="6" t="s"/>
+      <x:c r="D80" s="8" t="s"/>
+      <x:c r="E80" s="8" t="s"/>
+      <x:c r="F80" s="8" t="s"/>
       <x:c r="G80" s="2" t="s"/>
       <x:c r="H80" s="2" t="s"/>
       <x:c r="I80" s="2" t="s"/>
@@ -6094,11 +6177,11 @@
     </x:row>
     <x:row r="81" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A81" s="5" t="s"/>
-      <x:c r="B81" s="7" t="s"/>
+      <x:c r="B81" s="5" t="s"/>
       <x:c r="C81" s="6" t="s"/>
-      <x:c r="D81" s="8" t="s"/>
-      <x:c r="E81" s="8" t="s"/>
-      <x:c r="F81" s="8" t="s"/>
+      <x:c r="D81" s="6" t="s"/>
+      <x:c r="E81" s="6" t="s"/>
+      <x:c r="F81" s="6" t="s"/>
       <x:c r="G81" s="2" t="s"/>
       <x:c r="H81" s="2" t="s"/>
       <x:c r="I81" s="2" t="s"/>
@@ -6167,7 +6250,7 @@
     </x:row>
     <x:row r="82" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A82" s="5" t="s"/>
-      <x:c r="B82" s="5" t="s"/>
+      <x:c r="B82" s="6" t="s"/>
       <x:c r="C82" s="6" t="s"/>
       <x:c r="D82" s="6" t="s"/>
       <x:c r="E82" s="6" t="s"/>
@@ -6824,20 +6907,20 @@
     </x:row>
     <x:row r="91" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <x:c r="A91" s="5" t="s"/>
-      <x:c r="B91" s="6" t="s"/>
-      <x:c r="C91" s="6" t="s"/>
-      <x:c r="D91" s="6" t="s"/>
-      <x:c r="E91" s="6" t="s"/>
-      <x:c r="F91" s="6" t="s"/>
-      <x:c r="G91" s="2" t="s"/>
-      <x:c r="H91" s="2" t="s"/>
-      <x:c r="I91" s="2" t="s"/>
-      <x:c r="J91" s="2" t="s"/>
-      <x:c r="K91" s="2" t="s"/>
-      <x:c r="L91" s="2" t="s"/>
-      <x:c r="M91" s="2" t="s"/>
-      <x:c r="N91" s="2" t="s"/>
-      <x:c r="O91" s="2" t="s"/>
+      <x:c r="B91" s="5" t="s"/>
+      <x:c r="C91" s="5" t="s"/>
+      <x:c r="D91" s="5" t="s"/>
+      <x:c r="E91" s="5" t="s"/>
+      <x:c r="F91" s="5" t="s"/>
+      <x:c r="G91" s="1" t="s"/>
+      <x:c r="H91" s="1" t="s"/>
+      <x:c r="I91" s="1" t="s"/>
+      <x:c r="J91" s="1" t="s"/>
+      <x:c r="K91" s="1" t="s"/>
+      <x:c r="L91" s="1" t="s"/>
+      <x:c r="M91" s="1" t="s"/>
+      <x:c r="N91" s="1" t="s"/>
+      <x:c r="O91" s="1" t="s"/>
       <x:c r="P91" s="1" t="s"/>
       <x:c r="Q91" s="1" t="s"/>
       <x:c r="R91" s="1" t="s"/>
@@ -16969,78 +17052,64 @@
       <x:c r="BR229" s="5" t="s"/>
       <x:c r="BS229" s="5" t="s"/>
     </x:row>
-    <x:row r="230" spans="1:71" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <x:c r="A230" s="5" t="s"/>
-      <x:c r="B230" s="5" t="s"/>
-      <x:c r="C230" s="5" t="s"/>
-      <x:c r="D230" s="5" t="s"/>
-      <x:c r="E230" s="5" t="s"/>
-      <x:c r="F230" s="5" t="s"/>
-      <x:c r="G230" s="1" t="s"/>
-      <x:c r="H230" s="1" t="s"/>
-      <x:c r="I230" s="1" t="s"/>
-      <x:c r="J230" s="1" t="s"/>
-      <x:c r="K230" s="1" t="s"/>
-      <x:c r="L230" s="1" t="s"/>
-      <x:c r="M230" s="1" t="s"/>
-      <x:c r="N230" s="1" t="s"/>
-      <x:c r="O230" s="1" t="s"/>
-      <x:c r="P230" s="1" t="s"/>
-      <x:c r="Q230" s="1" t="s"/>
-      <x:c r="R230" s="1" t="s"/>
-      <x:c r="S230" s="1" t="s"/>
-      <x:c r="T230" s="1" t="s"/>
-      <x:c r="U230" s="1" t="s"/>
-      <x:c r="V230" s="1" t="s"/>
-      <x:c r="W230" s="1" t="s"/>
-      <x:c r="X230" s="1" t="s"/>
-      <x:c r="Y230" s="1" t="s"/>
-      <x:c r="Z230" s="1" t="s"/>
-      <x:c r="AA230" s="1" t="s"/>
-      <x:c r="AB230" s="1" t="s"/>
-      <x:c r="AC230" s="1" t="s"/>
-      <x:c r="AD230" s="1" t="s"/>
-      <x:c r="AE230" s="1" t="s"/>
-      <x:c r="AF230" s="1" t="s"/>
-      <x:c r="AG230" s="1" t="s"/>
-      <x:c r="AH230" s="1" t="s"/>
-      <x:c r="AI230" s="1" t="s"/>
-      <x:c r="AJ230" s="1" t="s"/>
-      <x:c r="AK230" s="1" t="s"/>
-      <x:c r="AL230" s="1" t="s"/>
-      <x:c r="AM230" s="1" t="s"/>
-      <x:c r="AN230" s="1" t="s"/>
-      <x:c r="AO230" s="1" t="s"/>
-      <x:c r="AP230" s="1" t="s"/>
-      <x:c r="AQ230" s="1" t="s"/>
-      <x:c r="AR230" s="1" t="s"/>
-      <x:c r="AS230" s="1" t="s"/>
-      <x:c r="AT230" s="1" t="s"/>
-      <x:c r="AU230" s="1" t="s"/>
-      <x:c r="AV230" s="1" t="s"/>
-      <x:c r="AW230" s="1" t="s"/>
-      <x:c r="AX230" s="1" t="s"/>
-      <x:c r="AY230" s="1" t="s"/>
-      <x:c r="AZ230" s="1" t="s"/>
-      <x:c r="BA230" s="1" t="s"/>
-      <x:c r="BB230" s="1" t="s"/>
-      <x:c r="BC230" s="1" t="s"/>
-      <x:c r="BD230" s="1" t="s"/>
-      <x:c r="BE230" s="1" t="s"/>
-      <x:c r="BF230" s="1" t="s"/>
-      <x:c r="BG230" s="1" t="s"/>
-      <x:c r="BH230" s="1" t="s"/>
-      <x:c r="BI230" s="1" t="s"/>
-      <x:c r="BJ230" s="1" t="s"/>
-      <x:c r="BK230" s="1" t="s"/>
-      <x:c r="BL230" s="5" t="s"/>
-      <x:c r="BM230" s="5" t="s"/>
-      <x:c r="BN230" s="5" t="s"/>
-      <x:c r="BO230" s="5" t="s"/>
-      <x:c r="BP230" s="5" t="s"/>
-      <x:c r="BQ230" s="5" t="s"/>
-      <x:c r="BR230" s="5" t="s"/>
-      <x:c r="BS230" s="5" t="s"/>
+    <x:row r="230" spans="1:71" x14ac:dyDescent="0.3">
+      <x:c r="G230" s="4" t="s"/>
+      <x:c r="H230" s="4" t="s"/>
+      <x:c r="I230" s="4" t="s"/>
+      <x:c r="J230" s="4" t="s"/>
+      <x:c r="K230" s="4" t="s"/>
+      <x:c r="L230" s="4" t="s"/>
+      <x:c r="M230" s="4" t="s"/>
+      <x:c r="N230" s="4" t="s"/>
+      <x:c r="O230" s="4" t="s"/>
+      <x:c r="P230" s="4" t="s"/>
+      <x:c r="Q230" s="4" t="s"/>
+      <x:c r="R230" s="4" t="s"/>
+      <x:c r="S230" s="4" t="s"/>
+      <x:c r="T230" s="4" t="s"/>
+      <x:c r="U230" s="4" t="s"/>
+      <x:c r="V230" s="4" t="s"/>
+      <x:c r="W230" s="4" t="s"/>
+      <x:c r="X230" s="4" t="s"/>
+      <x:c r="Y230" s="4" t="s"/>
+      <x:c r="Z230" s="4" t="s"/>
+      <x:c r="AA230" s="4" t="s"/>
+      <x:c r="AB230" s="4" t="s"/>
+      <x:c r="AC230" s="4" t="s"/>
+      <x:c r="AD230" s="4" t="s"/>
+      <x:c r="AE230" s="4" t="s"/>
+      <x:c r="AF230" s="4" t="s"/>
+      <x:c r="AG230" s="4" t="s"/>
+      <x:c r="AH230" s="4" t="s"/>
+      <x:c r="AI230" s="4" t="s"/>
+      <x:c r="AJ230" s="4" t="s"/>
+      <x:c r="AK230" s="4" t="s"/>
+      <x:c r="AL230" s="4" t="s"/>
+      <x:c r="AM230" s="4" t="s"/>
+      <x:c r="AN230" s="4" t="s"/>
+      <x:c r="AO230" s="4" t="s"/>
+      <x:c r="AP230" s="4" t="s"/>
+      <x:c r="AQ230" s="4" t="s"/>
+      <x:c r="AR230" s="4" t="s"/>
+      <x:c r="AS230" s="4" t="s"/>
+      <x:c r="AT230" s="4" t="s"/>
+      <x:c r="AU230" s="4" t="s"/>
+      <x:c r="AV230" s="4" t="s"/>
+      <x:c r="AW230" s="4" t="s"/>
+      <x:c r="AX230" s="4" t="s"/>
+      <x:c r="AY230" s="4" t="s"/>
+      <x:c r="AZ230" s="4" t="s"/>
+      <x:c r="BA230" s="4" t="s"/>
+      <x:c r="BB230" s="4" t="s"/>
+      <x:c r="BC230" s="4" t="s"/>
+      <x:c r="BD230" s="4" t="s"/>
+      <x:c r="BE230" s="4" t="s"/>
+      <x:c r="BF230" s="4" t="s"/>
+      <x:c r="BG230" s="4" t="s"/>
+      <x:c r="BH230" s="4" t="s"/>
+      <x:c r="BI230" s="4" t="s"/>
+      <x:c r="BJ230" s="4" t="s"/>
+      <x:c r="BK230" s="4" t="s"/>
     </x:row>
     <x:row r="231" spans="1:71" x14ac:dyDescent="0.3">
       <x:c r="G231" s="4" t="s"/>
@@ -17219,65 +17288,6 @@
       <x:c r="BJ233" s="4" t="s"/>
       <x:c r="BK233" s="4" t="s"/>
     </x:row>
-    <x:row r="234" spans="1:71" x14ac:dyDescent="0.3">
-      <x:c r="G234" s="4" t="s"/>
-      <x:c r="H234" s="4" t="s"/>
-      <x:c r="I234" s="4" t="s"/>
-      <x:c r="J234" s="4" t="s"/>
-      <x:c r="K234" s="4" t="s"/>
-      <x:c r="L234" s="4" t="s"/>
-      <x:c r="M234" s="4" t="s"/>
-      <x:c r="N234" s="4" t="s"/>
-      <x:c r="O234" s="4" t="s"/>
-      <x:c r="P234" s="4" t="s"/>
-      <x:c r="Q234" s="4" t="s"/>
-      <x:c r="R234" s="4" t="s"/>
-      <x:c r="S234" s="4" t="s"/>
-      <x:c r="T234" s="4" t="s"/>
-      <x:c r="U234" s="4" t="s"/>
-      <x:c r="V234" s="4" t="s"/>
-      <x:c r="W234" s="4" t="s"/>
-      <x:c r="X234" s="4" t="s"/>
-      <x:c r="Y234" s="4" t="s"/>
-      <x:c r="Z234" s="4" t="s"/>
-      <x:c r="AA234" s="4" t="s"/>
-      <x:c r="AB234" s="4" t="s"/>
-      <x:c r="AC234" s="4" t="s"/>
-      <x:c r="AD234" s="4" t="s"/>
-      <x:c r="AE234" s="4" t="s"/>
-      <x:c r="AF234" s="4" t="s"/>
-      <x:c r="AG234" s="4" t="s"/>
-      <x:c r="AH234" s="4" t="s"/>
-      <x:c r="AI234" s="4" t="s"/>
-      <x:c r="AJ234" s="4" t="s"/>
-      <x:c r="AK234" s="4" t="s"/>
-      <x:c r="AL234" s="4" t="s"/>
-      <x:c r="AM234" s="4" t="s"/>
-      <x:c r="AN234" s="4" t="s"/>
-      <x:c r="AO234" s="4" t="s"/>
-      <x:c r="AP234" s="4" t="s"/>
-      <x:c r="AQ234" s="4" t="s"/>
-      <x:c r="AR234" s="4" t="s"/>
-      <x:c r="AS234" s="4" t="s"/>
-      <x:c r="AT234" s="4" t="s"/>
-      <x:c r="AU234" s="4" t="s"/>
-      <x:c r="AV234" s="4" t="s"/>
-      <x:c r="AW234" s="4" t="s"/>
-      <x:c r="AX234" s="4" t="s"/>
-      <x:c r="AY234" s="4" t="s"/>
-      <x:c r="AZ234" s="4" t="s"/>
-      <x:c r="BA234" s="4" t="s"/>
-      <x:c r="BB234" s="4" t="s"/>
-      <x:c r="BC234" s="4" t="s"/>
-      <x:c r="BD234" s="4" t="s"/>
-      <x:c r="BE234" s="4" t="s"/>
-      <x:c r="BF234" s="4" t="s"/>
-      <x:c r="BG234" s="4" t="s"/>
-      <x:c r="BH234" s="4" t="s"/>
-      <x:c r="BI234" s="4" t="s"/>
-      <x:c r="BJ234" s="4" t="s"/>
-      <x:c r="BK234" s="4" t="s"/>
-    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17285,4 +17295,10 @@
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0a48d209-cb37-45d6-832d-49f966cbeefa}" enabled="1" method="Standard" siteId="{c3d90467-3ded-4815-aba1-a849ffa95164}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>